--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -158,6 +158,81 @@
   </si>
   <si>
     <t>返回</t>
+  </si>
+  <si>
+    <t>UI_Settings.Back</t>
+  </si>
+  <si>
+    <t>UI_Settings.Common</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>常规</t>
+  </si>
+  <si>
+    <t>UI_Settings.Input</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>UI_Settings.ScreenSize</t>
+  </si>
+  <si>
+    <t>Screen Size</t>
+  </si>
+  <si>
+    <t>分辨率</t>
+  </si>
+  <si>
+    <t>UI_Settings.FullScreen</t>
+  </si>
+  <si>
+    <t>Full Screen</t>
+  </si>
+  <si>
+    <t>全屏</t>
+  </si>
+  <si>
+    <t>UI_Settings.MusicVolume</t>
+  </si>
+  <si>
+    <t>Music Volume</t>
+  </si>
+  <si>
+    <t>背景音量</t>
+  </si>
+  <si>
+    <t>UI_Settings.SoundVolume</t>
+  </si>
+  <si>
+    <t>Sound Volume</t>
+  </si>
+  <si>
+    <t>音效音量</t>
+  </si>
+  <si>
+    <t>UI_Settings.Language</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>语言</t>
+  </si>
+  <si>
+    <t>UI_Settings.Reset</t>
+  </si>
+  <si>
+    <t>Reset to Defualt</t>
+  </si>
+  <si>
+    <t>重置默认</t>
   </si>
 </sst>
 </file>
@@ -1095,11 +1170,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="20.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.75" customWidth="1"/>
+    <col min="1" max="1" width="23.0833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
     <col min="3" max="3" width="10.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="7.33333333333333" customWidth="1"/>
   </cols>
@@ -1294,6 +1369,105 @@
         <v>47</v>
       </c>
     </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>Id</t>
   </si>
@@ -37,6 +37,9 @@
     <t>输入用户名</t>
   </si>
   <si>
+    <t>ユーザー名</t>
+  </si>
+  <si>
     <t>UI_Login.password</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t>输入密码</t>
   </si>
   <si>
+    <t>パスワード</t>
+  </si>
+  <si>
     <t>UI_Login.login</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t>登录</t>
   </si>
   <si>
+    <t>ログイン</t>
+  </si>
+  <si>
     <t>UI_Login.toregister</t>
   </si>
   <si>
@@ -64,6 +73,9 @@
     <t>去注册</t>
   </si>
   <si>
+    <t>行き登録</t>
+  </si>
+  <si>
     <t>UI_Login.password2</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
     <t>确认密码</t>
   </si>
   <si>
+    <t>暗証番号を確認</t>
+  </si>
+  <si>
     <t>UI_Login.register</t>
   </si>
   <si>
@@ -82,6 +97,9 @@
     <t>注册</t>
   </si>
   <si>
+    <t>登録</t>
+  </si>
+  <si>
     <t>UI_Login.tologin</t>
   </si>
   <si>
@@ -91,6 +109,9 @@
     <t>去登录</t>
   </si>
   <si>
+    <t>に登录</t>
+  </si>
+  <si>
     <t>UI_Lobby.Arcade</t>
   </si>
   <si>
@@ -100,6 +121,9 @@
     <t>剧情</t>
   </si>
   <si>
+    <t>ストーリー</t>
+  </si>
+  <si>
     <t>UI_Lobby.Match</t>
   </si>
   <si>
@@ -109,24 +133,36 @@
     <t>匹配</t>
   </si>
   <si>
+    <t>ふさわしい</t>
+  </si>
+  <si>
     <t>Training</t>
   </si>
   <si>
     <t>训练</t>
   </si>
   <si>
+    <t>トレーニング</t>
+  </si>
+  <si>
     <t>Replay</t>
   </si>
   <si>
     <t>回放</t>
   </si>
   <si>
+    <t>再生</t>
+  </si>
+  <si>
     <t>Settings</t>
   </si>
   <si>
     <t>设置</t>
   </si>
   <si>
+    <t>設置</t>
+  </si>
+  <si>
     <t>Exit</t>
   </si>
   <si>
@@ -142,6 +178,9 @@
     <t>已用时间：</t>
   </si>
   <si>
+    <t>すでに用时间:</t>
+  </si>
+  <si>
     <t>UI_Matching.Cancel</t>
   </si>
   <si>
@@ -151,6 +190,9 @@
     <t>取消</t>
   </si>
   <si>
+    <t>キャンセル</t>
+  </si>
+  <si>
     <t>UI_RoleSelect.Back</t>
   </si>
   <si>
@@ -160,6 +202,9 @@
     <t>返回</t>
   </si>
   <si>
+    <t>戻る</t>
+  </si>
+  <si>
     <t>UI_Settings.Back</t>
   </si>
   <si>
@@ -172,6 +217,9 @@
     <t>常规</t>
   </si>
   <si>
+    <t>通常</t>
+  </si>
+  <si>
     <t>UI_Settings.Input</t>
   </si>
   <si>
@@ -181,6 +229,9 @@
     <t>输入</t>
   </si>
   <si>
+    <t>入力</t>
+  </si>
+  <si>
     <t>UI_Settings.ScreenSize</t>
   </si>
   <si>
@@ -190,6 +241,9 @@
     <t>分辨率</t>
   </si>
   <si>
+    <t>解像度</t>
+  </si>
+  <si>
     <t>UI_Settings.FullScreen</t>
   </si>
   <si>
@@ -199,6 +253,9 @@
     <t>全屏</t>
   </si>
   <si>
+    <t>全般</t>
+  </si>
+  <si>
     <t>UI_Settings.MusicVolume</t>
   </si>
   <si>
@@ -208,6 +265,9 @@
     <t>背景音量</t>
   </si>
   <si>
+    <t>背景のボリューム</t>
+  </si>
+  <si>
     <t>UI_Settings.SoundVolume</t>
   </si>
   <si>
@@ -217,6 +277,9 @@
     <t>音效音量</t>
   </si>
   <si>
+    <t>サウンド音量</t>
+  </si>
+  <si>
     <t>UI_Settings.Language</t>
   </si>
   <si>
@@ -226,6 +289,9 @@
     <t>语言</t>
   </si>
   <si>
+    <t>言語</t>
+  </si>
+  <si>
     <t>UI_Settings.Reset</t>
   </si>
   <si>
@@ -233,6 +299,9 @@
   </si>
   <si>
     <t>重置默认</t>
+  </si>
+  <si>
+    <t>リセット黙認</t>
   </si>
 </sst>
 </file>
@@ -1176,6 +1245,7 @@
     <col min="1" max="1" width="23.0833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
     <col min="3" max="3" width="10.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.8333333333333" customWidth="1"/>
     <col min="5" max="5" width="7.33333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1193,7 +1263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1203,269 +1273,344 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>86</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>90</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24930" windowHeight="10730"/>
+    <workbookView windowWidth="24930" windowHeight="10130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>Id</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>リセット黙認</t>
+  </si>
+  <si>
+    <t>UI_Replay.Back</t>
+  </si>
+  <si>
+    <t>UI_Replay.Title</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="23.0833333333333" style="1" customWidth="1"/>
@@ -1613,6 +1619,34 @@
         <v>95</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24930" windowHeight="10130"/>
+    <workbookView windowWidth="24930" windowHeight="10730"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>Id</t>
   </si>
@@ -308,6 +308,18 @@
   </si>
   <si>
     <t>UI_Replay.Title</t>
+  </si>
+  <si>
+    <t>UI_Login.onauth</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>开始</t>
+  </si>
+  <si>
+    <t>開始する</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="23.0833333333333" style="1" customWidth="1"/>
@@ -1647,6 +1659,20 @@
         <v>45</v>
       </c>
     </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
